--- a/public/downloads/SandbergStrongly2018.xlsx
+++ b/public/downloads/SandbergStrongly2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>CO</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CHO</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
 </sst>
 </file>
@@ -656,10 +679,10 @@
         <v>56</v>
       </c>
       <c r="N3" s="5">
-        <v>277.2374172210693</v>
+        <v>277237.4172210693</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03257401212796021</v>
+        <v>32.57401212796021</v>
       </c>
       <c r="P3" s="5">
         <v>8511</v>
@@ -706,10 +729,10 @@
         <v>56</v>
       </c>
       <c r="N4" s="5">
-        <v>655.7755467891693</v>
+        <v>655775.5467891693</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06061892649188106</v>
+        <v>60.61892649188106</v>
       </c>
       <c r="P4" s="5">
         <v>10818</v>
@@ -756,10 +779,10 @@
         <v>56</v>
       </c>
       <c r="N5" s="5">
-        <v>5173.299681425095</v>
+        <v>5173299.681425095</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1426644884845043</v>
+        <v>142.6644884845043</v>
       </c>
       <c r="P5" s="5">
         <v>36262</v>
@@ -806,10 +829,10 @@
         <v>56</v>
       </c>
       <c r="N6" s="5">
-        <v>795.1707782745361</v>
+        <v>795170.7782745361</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08247803944347434</v>
+        <v>82.47803944347434</v>
       </c>
       <c r="P6" s="5">
         <v>9641</v>
@@ -856,10 +879,10 @@
         <v>56</v>
       </c>
       <c r="N7" s="5">
-        <v>1652.972114562988</v>
+        <v>1652972.114562988</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2334706376501396</v>
+        <v>233.4706376501396</v>
       </c>
       <c r="P7" s="5">
         <v>7080</v>
@@ -906,10 +929,10 @@
         <v>56</v>
       </c>
       <c r="N8" s="5">
-        <v>119.8951368331909</v>
+        <v>119895.1368331909</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01612143832636694</v>
+        <v>16.12143832636694</v>
       </c>
       <c r="P8" s="5">
         <v>7437</v>
@@ -956,10 +979,10 @@
         <v>56</v>
       </c>
       <c r="N9" s="5">
-        <v>356.2353641986847</v>
+        <v>356235.3641986847</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03043446084568003</v>
+        <v>30.43446084568003</v>
       </c>
       <c r="P9" s="5">
         <v>11705</v>
@@ -1006,10 +1029,10 @@
         <v>56</v>
       </c>
       <c r="N10" s="5">
-        <v>722.1877608299255</v>
+        <v>722187.7608299255</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08704203457031764</v>
+        <v>87.04203457031764</v>
       </c>
       <c r="P10" s="5">
         <v>8297</v>
@@ -1056,10 +1079,10 @@
         <v>56</v>
       </c>
       <c r="N11" s="5">
-        <v>477.3128094673157</v>
+        <v>477312.8094673157</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04653986051748397</v>
+        <v>46.53986051748397</v>
       </c>
       <c r="P11" s="5">
         <v>10256</v>
@@ -1106,10 +1129,10 @@
         <v>56</v>
       </c>
       <c r="N12" s="5">
-        <v>169.1293864250183</v>
+        <v>169129.3864250183</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02063308361900919</v>
+        <v>20.63308361900919</v>
       </c>
       <c r="P12" s="5">
         <v>8197</v>
@@ -1156,10 +1179,10 @@
         <v>56</v>
       </c>
       <c r="N13" s="5">
-        <v>584.4001457691193</v>
+        <v>584400.1457691193</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07384383949571889</v>
+        <v>73.8438394957189</v>
       </c>
       <c r="P13" s="5">
         <v>7914</v>
@@ -1206,10 +1229,10 @@
         <v>56</v>
       </c>
       <c r="N14" s="5">
-        <v>1709.693052530289</v>
+        <v>1709693.052530289</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3115329906214083</v>
+        <v>311.5329906214083</v>
       </c>
       <c r="P14" s="5">
         <v>5488</v>
@@ -1256,10 +1279,10 @@
         <v>56</v>
       </c>
       <c r="N15" s="5">
-        <v>2364.464767456055</v>
+        <v>2364464.767456055</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3079532127449928</v>
+        <v>307.9532127449928</v>
       </c>
       <c r="P15" s="5">
         <v>7678</v>
@@ -1306,10 +1329,10 @@
         <v>56</v>
       </c>
       <c r="N16" s="5">
-        <v>655.0537970066071</v>
+        <v>655053.7970066071</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09985576173881205</v>
+        <v>99.85576173881205</v>
       </c>
       <c r="P16" s="5">
         <v>6560</v>
@@ -1356,10 +1379,10 @@
         <v>56</v>
       </c>
       <c r="N17" s="5">
-        <v>871.8997159004211</v>
+        <v>871899.7159004211</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1101857343485936</v>
+        <v>110.1857343485936</v>
       </c>
       <c r="P17" s="5">
         <v>7913</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2876376150032693</v>
+        <v>0.759055775472237</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2683541108423227</v>
+        <v>0.7733894410278125</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2699814924308042</v>
+        <v>0.7015489050744784</v>
       </c>
       <c r="E3" s="4">
-        <v>77.16350826044733</v>
+        <v>81.93148688046649</v>
       </c>
       <c r="F3" s="4">
-        <v>82.45286033876437</v>
+        <v>81.69223394055595</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7733894410278125</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1480111672239472</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1439603864120927</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3382337105098639</v>
+        <v>0.6160556257541721</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3421126540155334</v>
+        <v>0.611709959699372</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3414361377558219</v>
+        <v>0.5877013834039381</v>
       </c>
       <c r="E4" s="4">
-        <v>78.29081632653073</v>
+        <v>82.49271137026254</v>
       </c>
       <c r="F4" s="4">
-        <v>82.26789709172026</v>
+        <v>85.39429530201284</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.611709959699372</v>
+      </c>
+      <c r="O4" s="5">
+        <v>27</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1537215356985654</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1549083092602012</v>
+      </c>
+      <c r="R4" s="5">
+        <v>27</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,34 +1735,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2795530232241227</v>
+        <v>0.9085150386853067</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2013749646406116</v>
+        <v>0.830328080457762</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2056817938667206</v>
+        <v>0.7238181940393977</v>
       </c>
       <c r="E3" s="4">
-        <v>74.54689018464548</v>
+        <v>70.44582118561699</v>
       </c>
       <c r="F3" s="4">
-        <v>77.44926494087555</v>
+        <v>69.91570789389586</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
         <v>7</v>
@@ -1670,50 +1794,86 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.830328080457762</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3426841564862589</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3274369513718987</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4110963161473202</v>
+        <v>0.5179176040770211</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3885604853612676</v>
+        <v>0.5040454748695166</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3877032765567492</v>
+        <v>0.4576092153147329</v>
       </c>
       <c r="E4" s="4">
-        <v>74.18731778425681</v>
+        <v>72.23517978620021</v>
       </c>
       <c r="F4" s="4">
-        <v>70.50215723873568</v>
+        <v>76.09020453818979</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.4879853688914657</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2923449970866941</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3265956598612425</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1884,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,91 +1976,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4112710537332792</v>
+        <v>0.3382337105098639</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3850806209175062</v>
+        <v>0.3421126540155334</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4165813848054053</v>
+        <v>0.3414361377558219</v>
       </c>
       <c r="E3" s="4">
-        <v>76.14917395529656</v>
+        <v>78.29081632653073</v>
       </c>
       <c r="F3" s="4">
-        <v>82.7660594439115</v>
+        <v>82.26789709172026</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3152475673221927</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1587038622835759</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1245230045932085</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5126032599628161</v>
+        <v>0.2876376150032693</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5282166185149365</v>
+        <v>0.2683541108423227</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5043049480480997</v>
+        <v>0.2699814924308042</v>
       </c>
       <c r="E4" s="4">
-        <v>76.60592808551999</v>
+        <v>77.16350826044733</v>
       </c>
       <c r="F4" s="4">
-        <v>82.05377117289839</v>
+        <v>82.45286033876437</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2403603814510295</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1925930255066777</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1574687564296326</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2125,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,91 +2217,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5453540658854763</v>
+        <v>0.4110963161473202</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5537152811605969</v>
+        <v>0.3885604853612676</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5717997493764935</v>
+        <v>0.3877032765567492</v>
       </c>
       <c r="E3" s="4">
-        <v>80.26239067055386</v>
+        <v>74.18731778425681</v>
       </c>
       <c r="F3" s="4">
-        <v>84.41155321188995</v>
+        <v>70.50215723873568</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3885604853612676</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1652335933651687</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1240942630395239</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8699756847931245</v>
+        <v>0.2795530232241227</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9230500976990151</v>
+        <v>0.2013749646406116</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9024661890345149</v>
+        <v>0.2056817938667206</v>
       </c>
       <c r="E4" s="4">
-        <v>80.84183673469354</v>
+        <v>74.54689018464548</v>
       </c>
       <c r="F4" s="4">
-        <v>83.33772770853481</v>
+        <v>77.44926494087555</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1293829350321349</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2518387736500842</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1582615397308395</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2366,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1327621418255995</v>
+        <v>0.5126032599628161</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1162340263076247</v>
+        <v>0.5282166185149365</v>
       </c>
       <c r="D3" s="4">
-        <v>0.120401967084588</v>
+        <v>0.5043049480480997</v>
       </c>
       <c r="E3" s="4">
-        <v>90.97789115646272</v>
+        <v>76.60592808551999</v>
       </c>
       <c r="F3" s="4">
-        <v>91.9926494087568</v>
+        <v>82.05377117289839</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5282166185149365</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1626697074447153</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1583683757304867</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1806058961235409</v>
+        <v>0.4112710537332792</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1575063497222634</v>
+        <v>0.3850806209175062</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1641397924172288</v>
+        <v>0.4165813848054053</v>
       </c>
       <c r="E4" s="4">
-        <v>90.66569484936839</v>
+        <v>76.14917395529656</v>
       </c>
       <c r="F4" s="4">
-        <v>90.62240332374486</v>
+        <v>82.7660594439115</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.3761823250285185</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1515246377160414</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1363070321145743</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2607,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,91 +2699,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.536315650760262</v>
+        <v>0.8699756847931245</v>
       </c>
       <c r="C3" s="4">
-        <v>0.536315650760262</v>
+        <v>0.9230500976990151</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5368339602979584</v>
+        <v>0.9024661890345149</v>
       </c>
       <c r="E3" s="4">
-        <v>80.07167152575317</v>
+        <v>80.84183673469354</v>
       </c>
       <c r="F3" s="4">
-        <v>85.76062639821036</v>
+        <v>83.33772770853481</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9230500976990151</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1650191219093072</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1160284938268596</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6109453593228459</v>
+        <v>0.5453540658854763</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5993489803559393</v>
+        <v>0.5537152811605969</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6035102614315645</v>
+        <v>0.5717997493764935</v>
       </c>
       <c r="E4" s="4">
-        <v>79.31486880466477</v>
+        <v>80.26239067055386</v>
       </c>
       <c r="F4" s="4">
-        <v>83.82909875359555</v>
+        <v>84.41155321188995</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.5537152811605969</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2067954281191349</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1909822037346708</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2867,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2909,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,91 +2940,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1541199647014924</v>
+        <v>0.1806058961235409</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1222890070581495</v>
+        <v>0.1575063497222634</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1562499694570886</v>
+        <v>0.1641397924172288</v>
       </c>
       <c r="E3" s="4">
-        <v>88.2847424684159</v>
+        <v>90.66569484936839</v>
       </c>
       <c r="F3" s="4">
-        <v>90.99912112495974</v>
+        <v>90.62240332374486</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1335489657331911</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1534435931463653</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1385276361878582</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1981272487751504</v>
+        <v>0.1327621418255995</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1489340364127492</v>
+        <v>0.1162340263076247</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2003679619287567</v>
+        <v>0.120401967084588</v>
       </c>
       <c r="E4" s="4">
-        <v>87.76846452866852</v>
+        <v>90.97789115646272</v>
       </c>
       <c r="F4" s="4">
-        <v>90.23170341962251</v>
+        <v>91.9926494087568</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.06531550249740389</v>
+      </c>
+      <c r="O4" s="5">
+        <v>27</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1323642713834689</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.118240512608282</v>
+      </c>
+      <c r="R4" s="5">
+        <v>27</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3089,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3108,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3150,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,91 +3181,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5604051516446779</v>
+        <v>0.6109453593228459</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5883905842370981</v>
+        <v>0.5993489803559393</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5412472486173855</v>
+        <v>0.6035102614315645</v>
       </c>
       <c r="E3" s="4">
-        <v>77.95189504373165</v>
+        <v>79.31486880466477</v>
       </c>
       <c r="F3" s="4">
-        <v>85.41267178012102</v>
+        <v>83.82909875359555</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5993489803559393</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1222807039504719</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.119198503828455</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4256444615347167</v>
+        <v>0.536315650760262</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4147772651970634</v>
+        <v>0.536315650760262</v>
       </c>
       <c r="D4" s="4">
-        <v>0.390325671264987</v>
+        <v>0.5368339602979584</v>
       </c>
       <c r="E4" s="4">
-        <v>77.59353741496592</v>
+        <v>80.07167152575317</v>
       </c>
       <c r="F4" s="4">
-        <v>81.50806967082126</v>
+        <v>85.76062639821036</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.535997914550557</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1651290737499913</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1651290737499913</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3330,1352 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1981272487751504</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1489340364127492</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2003679619287567</v>
+      </c>
+      <c r="E3" s="4">
+        <v>87.76846452866852</v>
+      </c>
+      <c r="F3" s="4">
+        <v>90.23170341962251</v>
+      </c>
+      <c r="G3" s="5">
+        <v>28</v>
+      </c>
+      <c r="H3" s="5">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1189481097130116</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1856851390655945</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1542429267037693</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1541199647014924</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1222890070581495</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1562499694570886</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.2847424684159</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.99912112495974</v>
+      </c>
+      <c r="G4" s="5">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.06086408991140118</v>
+      </c>
+      <c r="O4" s="5">
+        <v>25</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1558671210323246</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1315495129380496</v>
+      </c>
+      <c r="R4" s="5">
+        <v>25</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4256444615347167</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4147772651970634</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.390325671264987</v>
+      </c>
+      <c r="E3" s="4">
+        <v>77.59353741496592</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.50806967082126</v>
+      </c>
+      <c r="G3" s="5">
+        <v>28</v>
+      </c>
+      <c r="H3" s="5">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4147772651970634</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1815404730439001</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1579718886952313</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5604051516446779</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5883905842370981</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5412472486173855</v>
+      </c>
+      <c r="E4" s="4">
+        <v>77.95189504373165</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.41267178012102</v>
+      </c>
+      <c r="G4" s="5">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5814198784635309</v>
+      </c>
+      <c r="O4" s="5">
+        <v>25</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.268040128271355</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2624666072392439</v>
+      </c>
+      <c r="R4" s="5">
+        <v>25</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>80.35714285714286</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1961093791819678</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1488258776653158</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1681899589975813</v>
+      </c>
+      <c r="K3" s="4">
+        <v>79.16423712342068</v>
+      </c>
+      <c r="L3" s="4">
+        <v>81.10498561840622</v>
+      </c>
+      <c r="M3" s="5">
+        <v>56</v>
+      </c>
+      <c r="N3" s="5">
+        <v>277237.4172210693</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.57401212796021</v>
+      </c>
+      <c r="P3" s="5">
+        <v>8511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D4" s="3">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2921717969535699</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2564663532682934</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2373962390357157</v>
+      </c>
+      <c r="K4" s="4">
+        <v>69.42966472303212</v>
+      </c>
+      <c r="L4" s="4">
+        <v>74.13191115372244</v>
+      </c>
+      <c r="M4" s="5">
+        <v>56</v>
+      </c>
+      <c r="N4" s="5">
+        <v>655775.5467891693</v>
+      </c>
+      <c r="O4" s="4">
+        <v>60.61892649188106</v>
+      </c>
+      <c r="P4" s="5">
+        <v>10818</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>33.92857142857143</v>
+      </c>
+      <c r="E5" s="3">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="F5" s="3">
+        <v>19.64285714285714</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>4.034058202198451</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1521449802943715</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.709260271003169</v>
+      </c>
+      <c r="K5" s="4">
+        <v>63.07155004859088</v>
+      </c>
+      <c r="L5" s="4">
+        <v>66.94091562799667</v>
+      </c>
+      <c r="M5" s="5">
+        <v>56</v>
+      </c>
+      <c r="N5" s="5">
+        <v>5173299.681425095</v>
+      </c>
+      <c r="O5" s="4">
+        <v>142.6644884845043</v>
+      </c>
+      <c r="P5" s="5">
+        <v>36262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>73.21428571428571</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.266257354921672</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2201475014853606</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2183982831928821</v>
+      </c>
+      <c r="K6" s="4">
+        <v>77.57410106899903</v>
+      </c>
+      <c r="L6" s="4">
+        <v>77.12048577820271</v>
+      </c>
+      <c r="M6" s="5">
+        <v>56</v>
+      </c>
+      <c r="N6" s="5">
+        <v>795170.7782745361</v>
+      </c>
+      <c r="O6" s="4">
+        <v>82.47803944347434</v>
+      </c>
+      <c r="P6" s="5">
+        <v>9641</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>91.07142857142857</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.156235880630055</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1445757702533898</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1409229653209318</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.37402818270166</v>
+      </c>
+      <c r="L7" s="4">
+        <v>85.89525407478627</v>
+      </c>
+      <c r="M7" s="5">
+        <v>56</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1652972.114562988</v>
+      </c>
+      <c r="O7" s="4">
+        <v>233.4706376501396</v>
+      </c>
+      <c r="P7" s="5">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>94.64285714285714</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1508663514612563</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1495376301271668</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1636931849399586</v>
+      </c>
+      <c r="K8" s="4">
+        <v>82.21209912536428</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.54326462128465</v>
+      </c>
+      <c r="M8" s="5">
+        <v>56</v>
+      </c>
+      <c r="N8" s="5">
+        <v>119895.1368331909</v>
+      </c>
+      <c r="O8" s="4">
+        <v>16.12143832636694</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D9" s="3">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3175145767864765</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3269623766735799</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3238569839156404</v>
+      </c>
+      <c r="K9" s="4">
+        <v>71.34050048590845</v>
+      </c>
+      <c r="L9" s="4">
+        <v>73.00295621604268</v>
+      </c>
+      <c r="M9" s="5">
+        <v>56</v>
+      </c>
+      <c r="N9" s="5">
+        <v>356235.3641986847</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.43446084568003</v>
+      </c>
+      <c r="P9" s="5">
+        <v>11705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1756484438951268</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.140336965474692</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.150093515076047</v>
+      </c>
+      <c r="K10" s="4">
+        <v>77.72716229348893</v>
+      </c>
+      <c r="L10" s="4">
+        <v>82.36037871524228</v>
+      </c>
+      <c r="M10" s="5">
+        <v>56</v>
+      </c>
+      <c r="N10" s="5">
+        <v>722187.7608299255</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.04203457031764</v>
+      </c>
+      <c r="P10" s="5">
+        <v>8297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="C11" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2085361835076264</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1434865011616219</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1644492279878711</v>
+      </c>
+      <c r="K11" s="4">
+        <v>74.36710398445102</v>
+      </c>
+      <c r="L11" s="4">
+        <v>73.97571108980566</v>
+      </c>
+      <c r="M11" s="5">
+        <v>56</v>
+      </c>
+      <c r="N11" s="5">
+        <v>477312.8094673157</v>
+      </c>
+      <c r="O11" s="4">
+        <v>46.53986051748397</v>
+      </c>
+      <c r="P11" s="5">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1570971725803783</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1477789307948488</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.15210266636252</v>
+      </c>
+      <c r="K12" s="4">
+        <v>76.37755102040811</v>
+      </c>
+      <c r="L12" s="4">
+        <v>82.40991530840535</v>
+      </c>
+      <c r="M12" s="5">
+        <v>56</v>
+      </c>
+      <c r="N12" s="5">
+        <v>169129.3864250183</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.63308361900919</v>
+      </c>
+      <c r="P12" s="5">
+        <v>8197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.185907275014221</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1527405150061957</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1499202904149717</v>
+      </c>
+      <c r="K13" s="4">
+        <v>80.55211370262327</v>
+      </c>
+      <c r="L13" s="4">
+        <v>83.87464046021316</v>
+      </c>
+      <c r="M13" s="5">
+        <v>56</v>
+      </c>
+      <c r="N13" s="5">
+        <v>584400.1457691193</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.8438394957189</v>
+      </c>
+      <c r="P13" s="5">
+        <v>7914</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>94.64285714285714</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1429039322649171</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1281926864397722</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1307432287250355</v>
+      </c>
+      <c r="K14" s="4">
+        <v>90.8217930029156</v>
+      </c>
+      <c r="L14" s="4">
+        <v>91.30752636625232</v>
+      </c>
+      <c r="M14" s="5">
+        <v>56</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1709693.052530289</v>
+      </c>
+      <c r="O14" s="4">
+        <v>311.5329906214083</v>
+      </c>
+      <c r="P14" s="5">
+        <v>5488</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>96.42857142857143</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1437048888502316</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1430143548988813</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1518156033181124</v>
+      </c>
+      <c r="K15" s="4">
+        <v>79.69327016520897</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.79486257590308</v>
+      </c>
+      <c r="M15" s="5">
+        <v>56</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2364464.767456055</v>
+      </c>
+      <c r="O15" s="4">
+        <v>307.9532127449928</v>
+      </c>
+      <c r="P15" s="5">
+        <v>7678</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1707761300489596</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1426646543743205</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1740244154280306</v>
+      </c>
+      <c r="K16" s="4">
+        <v>88.02660349854202</v>
+      </c>
+      <c r="L16" s="4">
+        <v>90.61541227229134</v>
+      </c>
+      <c r="M16" s="5">
+        <v>56</v>
+      </c>
+      <c r="N16" s="5">
+        <v>655053.7970066071</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.85576173881205</v>
+      </c>
+      <c r="P16" s="5">
+        <v>6560</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8.928571428571429</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2247903006576275</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2102192479672375</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2324345447776674</v>
+      </c>
+      <c r="K17" s="4">
+        <v>77.77271622934884</v>
+      </c>
+      <c r="L17" s="4">
+        <v>83.46037072547176</v>
+      </c>
+      <c r="M17" s="5">
+        <v>56</v>
+      </c>
+      <c r="N17" s="5">
+        <v>871899.7159004211</v>
+      </c>
+      <c r="O17" s="4">
+        <v>110.1857343485936</v>
+      </c>
+      <c r="P17" s="5">
+        <v>7913</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2878,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -2963,16 +4877,16 @@
         <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3516,9 +5430,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>39</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>37</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>41</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>8</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>51</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>53</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>39</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>12</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>50</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>6</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>37</v>
+      </c>
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>50</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>49</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>7</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>53</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>54</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>49</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>7</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>5</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6198,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6240,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,40 +6271,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8452517366313259</v>
+        <v>1.146068248149797</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8205443360328156</v>
+        <v>1.197436827993363</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8542434771422579</v>
+        <v>1.166953114977072</v>
       </c>
       <c r="E3" s="4">
-        <v>78.85932944606424</v>
+        <v>79.46914480077741</v>
       </c>
       <c r="F3" s="4">
-        <v>81.25719079577939</v>
+        <v>80.95278044103296</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>5</v>
@@ -3629,40 +6330,58 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.197436827993363</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1863377033700462</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1438154127121145</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.146068248149797</v>
+        <v>0.8452517366313259</v>
       </c>
       <c r="C4" s="4">
-        <v>1.197436827993363</v>
+        <v>0.8205443360328156</v>
       </c>
       <c r="D4" s="4">
-        <v>1.166953114977072</v>
+        <v>0.8542434771422579</v>
       </c>
       <c r="E4" s="4">
-        <v>79.46914480077741</v>
+        <v>78.85932944606424</v>
       </c>
       <c r="F4" s="4">
-        <v>80.95278044103296</v>
+        <v>81.25719079577939</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>5</v>
@@ -3670,9 +6389,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.8205443360328156</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2058810549938893</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1540640910254808</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6420,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6439,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6481,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,91 +6512,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7440322410059578</v>
+        <v>1.097697899195996</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7380414607800049</v>
+        <v>1.127792625888871</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6918322642211153</v>
+        <v>1.07709216477958</v>
       </c>
       <c r="E3" s="4">
-        <v>69.05490767735672</v>
+        <v>69.8044217687076</v>
       </c>
       <c r="F3" s="4">
-        <v>75.49097155640683</v>
+        <v>72.77285075103768</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.127792625888871</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.334917633702184</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2909115010809317</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.097697899195996</v>
+        <v>0.7440322410059578</v>
       </c>
       <c r="C4" s="4">
-        <v>1.127792625888871</v>
+        <v>0.7380414607800049</v>
       </c>
       <c r="D4" s="4">
-        <v>1.07709216477958</v>
+        <v>0.6918322642211153</v>
       </c>
       <c r="E4" s="4">
-        <v>69.8044217687076</v>
+        <v>69.05490767735672</v>
       </c>
       <c r="F4" s="4">
-        <v>72.77285075103768</v>
+        <v>75.49097155640683</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.7380414607800049</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2494259602049559</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.223743462846287</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6661,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6680,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6722,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,91 +6753,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.422851704744452</v>
+        <v>6.882815204796576</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3373209240222316</v>
+        <v>0.5722855936573978</v>
       </c>
       <c r="D3" s="4">
-        <v>1.877708738179146</v>
+        <v>1.76067098954536</v>
       </c>
       <c r="E3" s="4">
-        <v>62.80855199222545</v>
+        <v>63.33454810495592</v>
       </c>
       <c r="F3" s="4">
-        <v>67.4616490891663</v>
+        <v>66.42018216682777</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
         <v>3</v>
       </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5722855936573978</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>6.690462790201634</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1423529859001064</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>6.882815204796576</v>
+        <v>1.422851704744452</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5722855936573978</v>
+        <v>0.3373209240222316</v>
       </c>
       <c r="D4" s="4">
-        <v>1.76067098954536</v>
+        <v>1.877708738179146</v>
       </c>
       <c r="E4" s="4">
-        <v>63.33454810495592</v>
+        <v>62.80855199222545</v>
       </c>
       <c r="F4" s="4">
-        <v>66.42018216682777</v>
+        <v>67.4616490891663</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
+        <v>11</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
         <v>8</v>
       </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.3373209240222316</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.377653614195267</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.163664973699389</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6902,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6921,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6963,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,91 +6994,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3086513681228098</v>
+        <v>0.5496279584480622</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2597998922233513</v>
+        <v>0.5783726487965892</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2560119002404723</v>
+        <v>0.545530415457506</v>
       </c>
       <c r="E3" s="4">
-        <v>77.8948007774539</v>
+        <v>77.25340136054452</v>
       </c>
       <c r="F3" s="4">
-        <v>77.6669862575888</v>
+        <v>76.57398529881574</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5783726487965892</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2630331069997136</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2384321860574483</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5496279584480622</v>
+        <v>0.3086513681228098</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5783726487965892</v>
+        <v>0.2597998922233513</v>
       </c>
       <c r="D4" s="4">
-        <v>0.545530415457506</v>
+        <v>0.2560119002404723</v>
       </c>
       <c r="E4" s="4">
-        <v>77.25340136054452</v>
+        <v>77.8948007774539</v>
       </c>
       <c r="F4" s="4">
-        <v>76.57398529881574</v>
+        <v>77.6669862575888</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2190645872580813</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2694816028436305</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1989757614545224</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7143,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7162,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7204,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,34 +7235,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3072517848876097</v>
+        <v>0.4288692074409742</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3220970201101199</v>
+        <v>0.439813479767472</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3361633555941808</v>
+        <v>0.4429503449619006</v>
       </c>
       <c r="E3" s="4">
-        <v>83.77793974732749</v>
+        <v>82.97011661807581</v>
       </c>
       <c r="F3" s="4">
-        <v>86.85242889102069</v>
+        <v>84.93807925854907</v>
       </c>
       <c r="G3" s="5">
         <v>28</v>
       </c>
       <c r="H3" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -4317,34 +7294,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.439813479767472</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1498702042372263</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1287047461598879</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4288692074409742</v>
+        <v>0.3072517848876097</v>
       </c>
       <c r="C4" s="4">
-        <v>0.439813479767472</v>
+        <v>0.3220970201101199</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4429503449619006</v>
+        <v>0.3361633555941808</v>
       </c>
       <c r="E4" s="4">
-        <v>82.97011661807581</v>
+        <v>83.77793974732749</v>
       </c>
       <c r="F4" s="4">
-        <v>84.93807925854907</v>
+        <v>86.85242889102069</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -4358,9 +7353,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.3128127108525055</v>
+      </c>
+      <c r="O4" s="5">
+        <v>26</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1626015570228836</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1598363703432956</v>
+      </c>
+      <c r="R4" s="5">
+        <v>26</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7384,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6160556257541721</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.611709959699372</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5877013834039381</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.49271137026254</v>
-      </c>
-      <c r="F3" s="4">
-        <v>85.39429530201284</v>
-      </c>
-      <c r="G3" s="5">
-        <v>28</v>
-      </c>
-      <c r="H3" s="5">
-        <v>27</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.759055775472237</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7733894410278125</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7015489050744784</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.93148688046649</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.69223394055595</v>
-      </c>
-      <c r="G4" s="5">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5">
-        <v>26</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5179176040770211</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5040454748695166</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4576092153147329</v>
-      </c>
-      <c r="E3" s="4">
-        <v>72.23517978620021</v>
-      </c>
-      <c r="F3" s="4">
-        <v>76.09020453818979</v>
-      </c>
-      <c r="G3" s="5">
-        <v>28</v>
-      </c>
-      <c r="H3" s="5">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9085150386853067</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.830328080457762</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7238181940393977</v>
-      </c>
-      <c r="E4" s="4">
-        <v>70.44582118561699</v>
-      </c>
-      <c r="F4" s="4">
-        <v>69.91570789389586</v>
-      </c>
-      <c r="G4" s="5">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SandbergStrongly2018.xlsx
+++ b/public/downloads/SandbergStrongly2018.xlsx
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7733894410278125</v>
+        <v>-0.7601066485482733</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1480111672239472</v>
+        <v>0.1466698463907658</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1439603864120927</v>
+        <v>0.1435376403209388</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.611709959699372</v>
+        <v>-0.6214587445909387</v>
       </c>
       <c r="O4" s="5">
         <v>27</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1537215356985654</v>
+        <v>0.1530251939205963</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1549083092602012</v>
+        <v>0.1545472431531061</v>
       </c>
       <c r="R4" s="5">
         <v>27</v>
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.830328080457762</v>
+        <v>-0.973351173393894</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3426841564862589</v>
+        <v>0.3254059074823609</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3274369513718987</v>
+        <v>0.3190238282580086</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -1854,16 +1854,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4879853688914657</v>
+        <v>-0.4697490051985369</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2923449970866941</v>
+        <v>0.2908937213932014</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3265956598612425</v>
+        <v>0.3256343445629516</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3152475673221927</v>
+        <v>-0.3363441302904979</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1587038622835759</v>
+        <v>0.1588005504891707</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1245230045932085</v>
+        <v>0.1230043178170563</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2403603814510295</v>
+        <v>-0.2499410774126751</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3885604853612676</v>
+        <v>-0.37478486308828</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1652335933651687</v>
+        <v>0.1657592490995999</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1240942630395239</v>
+        <v>0.1232922077906551</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -2336,16 +2336,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1293829350321349</v>
+        <v>-0.1194438083111891</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2518387736500842</v>
+        <v>0.2511288360271595</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1582615397308395</v>
+        <v>0.157788247982223</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2518,16 +2518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5282166185149365</v>
+        <v>-0.4962591940820857</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1626697074447153</v>
+        <v>0.1584019183601413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1583683757304867</v>
+        <v>0.1562305585957802</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -2577,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3761823250285185</v>
+        <v>-0.3929448441267596</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1515246377160414</v>
+        <v>0.1498927899192495</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1363070321145743</v>
+        <v>0.1358000862765039</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -2759,16 +2759,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9230500976990151</v>
+        <v>-0.8996704711316852</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1650191219093072</v>
+        <v>0.159768569415324</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1160284938268596</v>
+        <v>0.112953430221678</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -2818,16 +2818,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5537152811605969</v>
+        <v>-0.5725895967443648</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2067954281191349</v>
+        <v>0.2059185239829406</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1909822037346708</v>
+        <v>0.1899591489091108</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -3000,16 +3000,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1335489657331911</v>
+        <v>0.09720335127713042</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1534435931463653</v>
+        <v>0.1537794653968517</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1385276361878582</v>
+        <v>0.1360935282686851</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -3059,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06531550249740389</v>
+        <v>0.0185662794978505</v>
       </c>
       <c r="O4" s="5">
         <v>27</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1323642713834689</v>
+        <v>0.1299093371146533</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.118240512608282</v>
+        <v>0.1139632021443416</v>
       </c>
       <c r="R4" s="5">
         <v>27</v>
@@ -3241,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5993489803559393</v>
+        <v>-0.5592367445606286</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1222807039504719</v>
+        <v>0.122262308453918</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.119198503828455</v>
+        <v>0.1160931366940653</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -3300,16 +3300,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.535997914550557</v>
+        <v>-0.6114659905725262</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1651290737499913</v>
+        <v>0.1521138759479397</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1651290737499913</v>
+        <v>0.1521138759479397</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -3482,16 +3482,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1189481097130116</v>
+        <v>0.04853288754365792</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1856851390655945</v>
+        <v>0.1841480755388892</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1542429267037693</v>
+        <v>0.1407138155610541</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06086408991140118</v>
+        <v>0.01365436254133101</v>
       </c>
       <c r="O4" s="5">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1558671210323246</v>
+        <v>0.1518938597639864</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1315495129380496</v>
+        <v>0.1214342930331024</v>
       </c>
       <c r="R4" s="5">
         <v>25</v>
@@ -3723,16 +3723,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4147772651970634</v>
+        <v>-0.4434098987476318</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1815404730439001</v>
+        <v>0.1814790402070178</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1579718886952313</v>
+        <v>0.1568265833532085</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5814198784635309</v>
+        <v>-0.5611172059579985</v>
       </c>
       <c r="O4" s="5">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>0.268040128271355</v>
+        <v>0.2651397464848504</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2624666072392439</v>
+        <v>0.2616545003390226</v>
       </c>
       <c r="R4" s="5">
         <v>25</v>
@@ -3928,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1961093791819678</v>
+        <v>0.1948813080183364</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1488258776653158</v>
+        <v>0.1424173693427292</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1681899589975813</v>
+        <v>0.1654872524102627</v>
       </c>
       <c r="K3" s="4">
         <v>79.16423712342068</v>
@@ -3978,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2921717969535699</v>
+        <v>0.2904777884178397</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2564663532682934</v>
+        <v>0.2547459305628413</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2373962390357157</v>
+        <v>0.2411708365330014</v>
       </c>
       <c r="K4" s="4">
         <v>69.42966472303212</v>
@@ -4028,13 +4028,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>4.034058202198451</v>
+        <v>4.037314497195374</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1521449802943715</v>
+        <v>0.1505518013172322</v>
       </c>
       <c r="J5" s="4">
-        <v>1.709260271003169</v>
+        <v>1.715294268643382</v>
       </c>
       <c r="K5" s="4">
         <v>63.07155004859088</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.266257354921672</v>
+        <v>0.2581466975827555</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2201475014853606</v>
+        <v>0.2154536340592419</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2183982831928821</v>
+        <v>0.2173039446969856</v>
       </c>
       <c r="K6" s="4">
         <v>77.57410106899903</v>
@@ -4128,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.156235880630055</v>
+        <v>0.1549219709372665</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1445757702533898</v>
+        <v>0.142534937351336</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1409229653209318</v>
+        <v>0.1391542482765544</v>
       </c>
       <c r="K7" s="4">
         <v>83.37402818270166</v>
@@ -4178,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1508663514612563</v>
+        <v>0.149847520155681</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1495376301271668</v>
+        <v>0.1491463059146844</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1636931849399586</v>
+        <v>0.161794718482511</v>
       </c>
       <c r="K8" s="4">
         <v>82.21209912536428</v>
@@ -4228,13 +4228,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3175145767864765</v>
+        <v>0.3081498144377812</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3269623766735799</v>
+        <v>0.3227528374556688</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3238569839156404</v>
+        <v>0.3367515270168561</v>
       </c>
       <c r="K9" s="4">
         <v>71.34050048590845</v>
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1756484438951268</v>
+        <v>0.1756967879979242</v>
       </c>
       <c r="I10" s="4">
-        <v>0.140336965474692</v>
+        <v>0.1395472483510929</v>
       </c>
       <c r="J10" s="4">
-        <v>0.150093515076047</v>
+        <v>0.151371468782529</v>
       </c>
       <c r="K10" s="4">
         <v>77.72716229348893</v>
@@ -4328,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2085361835076264</v>
+        <v>0.2084440425633797</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1434865011616219</v>
+        <v>0.1428710414128963</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1644492279878711</v>
+        <v>0.1648619370209547</v>
       </c>
       <c r="K11" s="4">
         <v>74.36710398445102</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1570971725803783</v>
+        <v>0.1541473541396954</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1477789307948488</v>
+        <v>0.1464239318825275</v>
       </c>
       <c r="J12" s="4">
-        <v>0.15210266636252</v>
+        <v>0.1483192708850376</v>
       </c>
       <c r="K12" s="4">
         <v>76.37755102040811</v>
@@ -4428,13 +4428,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.185907275014221</v>
+        <v>0.1828435466991323</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1527405150061957</v>
+        <v>0.1506705169257267</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1499202904149717</v>
+        <v>0.1468797659814689</v>
       </c>
       <c r="K13" s="4">
         <v>80.55211370262327</v>
@@ -4478,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1429039322649171</v>
+        <v>0.1418444012557525</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1281926864397722</v>
+        <v>0.124819588544963</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1307432287250355</v>
+        <v>0.1294610701101602</v>
       </c>
       <c r="K14" s="4">
         <v>90.8217930029156</v>
@@ -4528,13 +4528,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1437048888502316</v>
+        <v>0.1371880922009288</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1430143548988813</v>
+        <v>0.1347705570479261</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1518156033181124</v>
+        <v>0.1485848797553055</v>
       </c>
       <c r="K15" s="4">
         <v>79.69327016520897</v>
@@ -4578,13 +4578,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1707761300489596</v>
+        <v>0.1680209676514378</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1426646543743205</v>
+        <v>0.1308773244753645</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1740244154280306</v>
+        <v>0.1742047821310025</v>
       </c>
       <c r="K16" s="4">
         <v>88.02660349854202</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2247903006576275</v>
+        <v>0.2233093933459341</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2102192479672375</v>
+        <v>0.2092405418461156</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2324345447776674</v>
+        <v>0.2330810095318479</v>
       </c>
       <c r="K17" s="4">
         <v>77.77271622934884</v>
@@ -6331,16 +6331,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.197436827993363</v>
+        <v>-1.251911058767291</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1863377033700462</v>
+        <v>0.1834918154195943</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1438154127121145</v>
+        <v>0.1332455190193128</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -6390,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8205443360328156</v>
+        <v>-0.7959063746639004</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2058810549938893</v>
+        <v>0.2062708006170786</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1540640910254808</v>
+        <v>0.1520061219535736</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -6572,16 +6572,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.127792625888871</v>
+        <v>-1.100024633400608</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.334917633702184</v>
+        <v>0.332934205667308</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2909115010809317</v>
+        <v>0.2894500277920758</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -6631,16 +6631,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7380414607800049</v>
+        <v>-0.7676133206732629</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2494259602049559</v>
+        <v>0.2480213711683713</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.223743462846287</v>
+        <v>0.2217770381950686</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -6813,13 +6813,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5722855936573978</v>
+        <v>-0.5698274683672935</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>6.690462790201634</v>
+        <v>6.68993604906804</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1423529859001064</v>
@@ -6872,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3373209240222316</v>
+        <v>-0.3885307027667295</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>1.377653614195267</v>
+        <v>1.384692945322708</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.163664973699389</v>
+        <v>0.1601974665138508</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -7054,16 +7054,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5783726487965892</v>
+        <v>-0.5091643562882382</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2630331069997136</v>
+        <v>0.2468117923218805</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2384321860574483</v>
+        <v>0.2298798854285864</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -7113,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2190645872580813</v>
+        <v>-0.2233625378939905</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
@@ -7122,7 +7122,7 @@
         <v>0.2694816028436305</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1989757614545224</v>
+        <v>0.1987495535263167</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -7295,16 +7295,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.439813479767472</v>
+        <v>-0.4094902381475549</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1498702042372263</v>
+        <v>0.1468039167686064</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1287047461598879</v>
+        <v>0.1264834338598303</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -7354,16 +7354,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3128127108525055</v>
+        <v>-0.343226099266758</v>
       </c>
       <c r="O4" s="5">
         <v>26</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1626015570228836</v>
+        <v>0.1630400251059265</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1598363703432956</v>
+        <v>0.1579690753239377</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
